--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FC BARCELONA.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FC BARCELONA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA48"/>
+  <dimension ref="A1:BA46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,13 +671,13 @@
         <v>0.2121460812474354</v>
       </c>
       <c r="J2" t="n">
-        <v>379</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>462</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>271</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
         <v>403</v>
@@ -752,13 +752,13 @@
         <v>1.117766497461929</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.768762677484787</v>
+        <v>0.01825557809330629</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.092198581560284</v>
+        <v>0.01654846335697399</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.709677419354839</v>
+        <v>2.5</v>
       </c>
       <c r="AN2" t="n">
         <v>1.517543859649123</v>
@@ -801,13 +801,13 @@
         <v>0.2121460812474354</v>
       </c>
       <c r="J3" t="n">
-        <v>9.973684210526315</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="K3" t="n">
-        <v>12.1578947368421</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="L3" t="n">
-        <v>7.131578947368421</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="M3" t="n">
         <v>10.60526315789474</v>
@@ -882,13 +882,13 @@
         <v>1.117766497461929</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.768762677484787</v>
+        <v>0.01825557809330629</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.092198581560283</v>
+        <v>0.01654846335697399</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.709677419354839</v>
+        <v>2.5</v>
       </c>
       <c r="AN3" t="n">
         <v>1.517543859649123</v>
@@ -931,16 +931,16 @@
         <v>0.2531155994843146</v>
       </c>
       <c r="J4" t="n">
-        <v>320</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>423</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>322</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N4" t="n">
         <v>1052</v>
@@ -1012,13 +1012,13 @@
         <v>1.067403314917127</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7017543859649122</v>
+        <v>0.03289473684210526</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.073604060913706</v>
+        <v>0.01015228426395939</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.737967914438503</v>
+        <v>2.2</v>
       </c>
       <c r="AN4" t="n">
         <v>1.334685598377282</v>
@@ -1061,16 +1061,16 @@
         <v>0.2531155994843146</v>
       </c>
       <c r="J5" t="n">
-        <v>8.421052631578947</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="K5" t="n">
-        <v>11.13157894736842</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="L5" t="n">
-        <v>8.473684210526315</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="M5" t="n">
-        <v>11.55263157894737</v>
+        <v>11.57894736842105</v>
       </c>
       <c r="N5" t="n">
         <v>27.68421052631579</v>
@@ -1142,13 +1142,13 @@
         <v>1.067403314917127</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7017543859649122</v>
+        <v>0.03289473684210526</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.073604060913706</v>
+        <v>0.01015228426395939</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.737967914438503</v>
+        <v>2.2</v>
       </c>
       <c r="AN5" t="n">
         <v>1.334685598377282</v>
@@ -1486,16 +1486,16 @@
         <v>533</v>
       </c>
       <c r="U8" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
         <v>132</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>1823:16</t>
+          <t>991:11</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>7.984</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.138</v>
+        <v>0.254</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.034</v>
+        <v>0.063</v>
       </c>
       <c r="BA8" t="n">
         <v>0.099</v>
@@ -1651,16 +1651,16 @@
         <v>44</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>5</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>575:38</t>
+          <t>246:25</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>5.778</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.014</v>
+        <v>0.034</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.039</v>
+        <v>0.091</v>
       </c>
       <c r="BA9" t="n">
         <v>0.034</v>
@@ -1816,16 +1816,16 @@
         <v>118</v>
       </c>
       <c r="U10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>27</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1180:54</t>
+          <t>510:48</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>14.111</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.049</v>
+        <v>0.112</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.026</v>
+        <v>0.06</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.041</v>
+        <v>0.095</v>
       </c>
       <c r="BA10" t="n">
         <v>0.021</v>
@@ -1981,16 +1981,16 @@
         <v>175</v>
       </c>
       <c r="U11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
         <v>29</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>935:52</t>
+          <t>416:15</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>13.778</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.065</v>
+        <v>0.145</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.038</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.073</v>
+        <v>0.165</v>
       </c>
       <c r="BA11" t="n">
         <v>0.01</v>
@@ -2146,16 +2146,16 @@
         <v>349</v>
       </c>
       <c r="U12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>76</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1382:57</t>
+          <t>756:34</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,13 +2235,13 @@
         <v>9.452</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.102</v>
+        <v>0.187</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.037</v>
+        <v>0.067</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.067</v>
+        <v>0.122</v>
       </c>
       <c r="BA12" t="n">
         <v>0.046</v>
@@ -2311,16 +2311,16 @@
         <v>238</v>
       </c>
       <c r="U13" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>51</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1238:21</t>
+          <t>555:34</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -2400,13 +2400,13 @@
         <v>9.879</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.125</v>
+        <v>0.278</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.035</v>
+        <v>0.078</v>
       </c>
       <c r="BA13" t="n">
         <v>0.049</v>
@@ -2476,16 +2476,16 @@
         <v>405</v>
       </c>
       <c r="U14" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="W14" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>1610:07</t>
+          <t>868:37</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2565,13 +2565,13 @@
         <v>6.612</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.133</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.022</v>
+        <v>0.041</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.073</v>
+        <v>0.135</v>
       </c>
       <c r="BA14" t="n">
         <v>0.139</v>
@@ -2641,16 +2641,16 @@
         <v>295</v>
       </c>
       <c r="U15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
         <v>112</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>994:12</t>
+          <t>495:09</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>4.132</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.107</v>
+        <v>0.216</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.061</v>
+        <v>0.122</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.113</v>
+        <v>0.226</v>
       </c>
       <c r="BA15" t="n">
         <v>0.015</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>25:16</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,7 +2895,7 @@
         <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.057</v>
+        <v>0.274</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -2974,13 +2974,13 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>20</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>230:00</t>
+          <t>129:09</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>17</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.075</v>
+        <v>0.134</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.125</v>
+        <v>0.222</v>
       </c>
       <c r="BA17" t="n">
         <v>0.003</v>
@@ -3136,16 +3136,16 @@
         <v>162</v>
       </c>
       <c r="U18" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>33</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>679:12</t>
+          <t>330:16</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>4.927</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.125</v>
+        <v>0.258</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.035</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="BA18" t="n">
         <v>0.06900000000000001</v>
@@ -3301,16 +3301,16 @@
         <v>453</v>
       </c>
       <c r="U19" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>120</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>1576:38</t>
+          <t>779:11</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>6.923</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.125</v>
+        <v>0.252</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.077</v>
+        <v>0.157</v>
       </c>
       <c r="BA19" t="n">
         <v>0.048</v>
@@ -3466,16 +3466,16 @@
         <v>539</v>
       </c>
       <c r="U20" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>171</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>1504:55</t>
+          <t>797:19</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3555,13 +3555,13 @@
         <v>5.915</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.119</v>
+        <v>0.225</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.038</v>
+        <v>0.073</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.079</v>
+        <v>0.148</v>
       </c>
       <c r="BA20" t="n">
         <v>0.083</v>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>101:42</t>
+          <t>50:12</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3720,13 +3720,13 @@
         <v>3.25</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.08</v>
+        <v>0.162</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.046</v>
+        <v>0.094</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.061</v>
+        <v>0.124</v>
       </c>
       <c r="BA21" t="n">
         <v>0.001</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>01:09</t>
+          <t>01:08</t>
         </is>
       </c>
       <c r="AO22" t="n">
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.418</v>
+        <v>0.424</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3961,16 +3961,16 @@
         <v>283</v>
       </c>
       <c r="U23" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>65</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1498:06</t>
+          <t>713:24</t>
         </is>
       </c>
       <c r="AO23" t="n">
@@ -4050,13 +4050,13 @@
         <v>9.952</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.068</v>
+        <v>0.142</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.038</v>
+        <v>0.079</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="BA23" t="n">
         <v>0.035</v>
@@ -4230,163 +4230,163 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>38</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>3221</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1459</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>978</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>657</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="T25" t="n">
-        <v>97</v>
+        <v>3794</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1072</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.836</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>753</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>0.482</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.404</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>0.468</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>899</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>0.366</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>7650:00</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>26</v>
+        <v>3182.08</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>0.555</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.012</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.518</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>5.344</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>6.862</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="BA25" t="n">
         <v>0</v>
@@ -4395,44 +4395,44 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>38</v>
       </c>
       <c r="C26" t="n">
-        <v>3221</v>
+        <v>3187</v>
       </c>
       <c r="D26" t="n">
-        <v>803</v>
+        <v>825</v>
       </c>
       <c r="E26" t="n">
-        <v>1459</v>
+        <v>1430</v>
       </c>
       <c r="F26" t="n">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="G26" t="n">
-        <v>978</v>
+        <v>897</v>
       </c>
       <c r="H26" t="n">
-        <v>517</v>
+        <v>589</v>
       </c>
       <c r="I26" t="n">
-        <v>657</v>
+        <v>751</v>
       </c>
       <c r="J26" t="n">
-        <v>692</v>
+        <v>658</v>
       </c>
       <c r="K26" t="n">
-        <v>834</v>
+        <v>872</v>
       </c>
       <c r="L26" t="n">
-        <v>423</v>
+        <v>394</v>
       </c>
       <c r="M26" t="n">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="N26" t="n">
         <v>148</v>
@@ -4441,76 +4441,76 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="Q26" t="n">
-        <v>403</v>
+        <v>440</v>
       </c>
       <c r="R26" t="n">
-        <v>708</v>
+        <v>721</v>
       </c>
       <c r="S26" t="n">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="T26" t="n">
-        <v>3794</v>
+        <v>3689</v>
       </c>
       <c r="U26" t="n">
-        <v>376</v>
+        <v>15</v>
       </c>
       <c r="V26" t="n">
-        <v>461</v>
+        <v>4</v>
       </c>
       <c r="W26" t="n">
-        <v>265</v>
+        <v>11</v>
       </c>
       <c r="X26" t="n">
-        <v>155</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>896</v>
+        <v>1044</v>
       </c>
       <c r="Z26" t="n">
-        <v>1072</v>
+        <v>1219</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.836</v>
+        <v>0.856</v>
       </c>
       <c r="AB26" t="n">
-        <v>363</v>
+        <v>336</v>
       </c>
       <c r="AC26" t="n">
-        <v>753</v>
+        <v>709</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.482</v>
+        <v>0.474</v>
       </c>
       <c r="AE26" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="AF26" t="n">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.404</v>
+        <v>0.374</v>
       </c>
       <c r="AH26" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AI26" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.468</v>
+        <v>0.402</v>
       </c>
       <c r="AK26" t="n">
-        <v>329</v>
+        <v>281</v>
       </c>
       <c r="AL26" t="n">
-        <v>899</v>
+        <v>810</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.366</v>
+        <v>0.347</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -4518,40 +4518,40 @@
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>3182.08</v>
+        <v>3150.44</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.555</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.591</v>
+        <v>0.6</v>
       </c>
       <c r="AR26" t="n">
         <v>1.012</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.143</v>
+        <v>0.156</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.212</v>
+        <v>0.253</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.518</v>
+        <v>1.335</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.344</v>
+        <v>4.72</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.862</v>
+        <v>6.055</v>
       </c>
       <c r="AX26" t="n">
         <v>0.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.136</v>
+        <v>0.135</v>
       </c>
       <c r="BA26" t="n">
         <v>0</v>
@@ -4560,601 +4560,601 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>38</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3187</v>
-      </c>
-      <c r="D27" t="n">
-        <v>825</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1430</v>
-      </c>
-      <c r="F27" t="n">
-        <v>316</v>
-      </c>
-      <c r="G27" t="n">
-        <v>897</v>
-      </c>
-      <c r="H27" t="n">
-        <v>589</v>
-      </c>
-      <c r="I27" t="n">
-        <v>751</v>
-      </c>
-      <c r="J27" t="n">
-        <v>658</v>
-      </c>
-      <c r="K27" t="n">
-        <v>872</v>
-      </c>
-      <c r="L27" t="n">
-        <v>394</v>
-      </c>
-      <c r="M27" t="n">
-        <v>227</v>
-      </c>
-      <c r="N27" t="n">
-        <v>148</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>493</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>439</v>
-      </c>
-      <c r="R27" t="n">
-        <v>721</v>
-      </c>
-      <c r="S27" t="n">
-        <v>765</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3689</v>
-      </c>
-      <c r="U27" t="n">
-        <v>315</v>
-      </c>
-      <c r="V27" t="n">
-        <v>418</v>
-      </c>
-      <c r="W27" t="n">
-        <v>325</v>
-      </c>
-      <c r="X27" t="n">
-        <v>187</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1044</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1219</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.856</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>336</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>709</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>91</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>35</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>87</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>281</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>810</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>7650:00</t>
-        </is>
-      </c>
-      <c r="AO27" t="n">
-        <v>3150.44</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.012</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.335</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>6.055</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr"/>
-      <c r="BA28" t="inlineStr"/>
+          <t>#0 K. PUNTER (Per Game)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>37</v>
+      </c>
+      <c r="C28" t="n">
+        <v>14.865</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6.162</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.811</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.324</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.622</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.703</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.324</v>
+      </c>
+      <c r="T28" t="n">
+        <v>533</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>3.568</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.054</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.811</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.811</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.919</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>4.649</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>26:47</t>
+        </is>
+      </c>
+      <c r="AO28" t="n">
+        <v>14.138</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>6.444</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7.984</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0.102</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#0 K. PUNTER (Per Game)</t>
+          <t>#2 J. MARCOS (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>14.865</v>
+        <v>1.781</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>0.188</v>
       </c>
       <c r="E29" t="n">
-        <v>6.162</v>
+        <v>0.625</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>0.469</v>
       </c>
       <c r="G29" t="n">
-        <v>4.811</v>
+        <v>1.406</v>
       </c>
       <c r="H29" t="n">
-        <v>2.865</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3.324</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>2.622</v>
+        <v>1.219</v>
       </c>
       <c r="K29" t="n">
-        <v>1.351</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>0.459</v>
+        <v>0.219</v>
       </c>
       <c r="M29" t="n">
-        <v>0.973</v>
+        <v>0.312</v>
       </c>
       <c r="N29" t="n">
-        <v>0.459</v>
+        <v>0.031</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.703</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.568</v>
+        <v>0.531</v>
       </c>
       <c r="R29" t="n">
-        <v>1.514</v>
+        <v>1.031</v>
       </c>
       <c r="S29" t="n">
-        <v>3.324</v>
+        <v>0.219</v>
       </c>
       <c r="T29" t="n">
-        <v>533</v>
+        <v>44</v>
       </c>
       <c r="U29" t="n">
-        <v>1.838</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.081</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.243</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>3.568</v>
+        <v>0.156</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.054</v>
+        <v>0.312</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.811</v>
+        <v>0.031</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.811</v>
+        <v>0.312</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.475</v>
+        <v>0.1</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.486</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.162</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.419</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.081</v>
+        <v>0.031</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.162</v>
+        <v>0.062</v>
       </c>
       <c r="AJ29" t="n">
         <v>0.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.919</v>
+        <v>0.438</v>
       </c>
       <c r="AL29" t="n">
-        <v>4.649</v>
+        <v>1.344</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.413</v>
+        <v>0.326</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>49:16</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>14.138</v>
+        <v>2.594</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.547</v>
+        <v>0.438</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.598</v>
+        <v>0.438</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.051</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.12</v>
+        <v>0.217</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.54</v>
+        <v>2.167</v>
       </c>
       <c r="AV29" t="n">
-        <v>6.444</v>
+        <v>3.611</v>
       </c>
       <c r="AW29" t="n">
-        <v>7.984</v>
+        <v>5.778</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.138</v>
+        <v>0.162</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.011</v>
+        <v>0.034</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.034</v>
+        <v>0.091</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.102</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#2 J. MARCOS (Per Game)</t>
+          <t>#3 M. CALE (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C30" t="n">
-        <v>1.781</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>0.188</v>
+        <v>0.676</v>
       </c>
       <c r="E30" t="n">
-        <v>0.625</v>
+        <v>1.297</v>
       </c>
       <c r="F30" t="n">
-        <v>0.469</v>
+        <v>0.432</v>
       </c>
       <c r="G30" t="n">
-        <v>1.406</v>
+        <v>1.486</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.459</v>
       </c>
       <c r="J30" t="n">
-        <v>1.219</v>
+        <v>0.649</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.054</v>
       </c>
       <c r="L30" t="n">
-        <v>0.219</v>
+        <v>0.703</v>
       </c>
       <c r="M30" t="n">
-        <v>0.312</v>
+        <v>0.459</v>
       </c>
       <c r="N30" t="n">
-        <v>0.031</v>
+        <v>0.216</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.243</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.531</v>
+        <v>0.216</v>
       </c>
       <c r="R30" t="n">
-        <v>1.031</v>
+        <v>1.649</v>
       </c>
       <c r="S30" t="n">
-        <v>0.219</v>
+        <v>0.784</v>
       </c>
       <c r="T30" t="n">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="U30" t="n">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0.531</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.156</v>
+        <v>0.73</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.312</v>
+        <v>0.865</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.5</v>
+        <v>0.844</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.031</v>
+        <v>0.27</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.312</v>
+        <v>0.703</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.1</v>
+        <v>0.385</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.031</v>
+        <v>0.108</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.062</v>
+        <v>0.324</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.438</v>
+        <v>0.324</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.344</v>
+        <v>1.162</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.326</v>
+        <v>0.279</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>2.594</v>
+        <v>3.229</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.438</v>
+        <v>0.476</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.438</v>
+        <v>0.502</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.929</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.217</v>
+        <v>0.075</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.167</v>
+        <v>2.667</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.611</v>
+        <v>11.444</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.778</v>
+        <v>14.111</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.014</v>
+        <v>0.06</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.039</v>
+        <v>0.095</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.04</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#3 M. CALE (Per Game)</t>
+          <t>#5 M. NORRIS (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>37</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>3.919</v>
       </c>
       <c r="D31" t="n">
-        <v>0.676</v>
+        <v>0.757</v>
       </c>
       <c r="E31" t="n">
-        <v>1.297</v>
+        <v>1.135</v>
       </c>
       <c r="F31" t="n">
-        <v>0.432</v>
+        <v>0.73</v>
       </c>
       <c r="G31" t="n">
+        <v>1.919</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="K31" t="n">
         <v>1.486</v>
       </c>
-      <c r="H31" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1.054</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.703</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>0.459</v>
+        <v>0.514</v>
       </c>
       <c r="N31" t="n">
-        <v>0.216</v>
+        <v>0.378</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -5163,823 +5163,823 @@
         <v>0.243</v>
       </c>
       <c r="Q31" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="S31" t="n">
         <v>0.216</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
+        <v>175</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="AL31" t="n">
         <v>1.649</v>
       </c>
-      <c r="S31" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="T31" t="n">
-        <v>118</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.162</v>
-      </c>
       <c r="AM31" t="n">
-        <v>0.279</v>
+        <v>0.393</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>31:54</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>3.229</v>
+        <v>3.404</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.476</v>
+        <v>0.606</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.502</v>
+        <v>0.62</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.929</v>
+        <v>1.151</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.075</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.126</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.667</v>
+        <v>1.222</v>
       </c>
       <c r="AV31" t="n">
-        <v>11.444</v>
+        <v>12.556</v>
       </c>
       <c r="AW31" t="n">
-        <v>14.111</v>
+        <v>13.778</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.049</v>
+        <v>0.145</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.026</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.041</v>
+        <v>0.165</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#5 M. NORRIS (Per Game)</t>
+          <t>#6 J. VESELY (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" t="n">
-        <v>3.919</v>
+        <v>8.667</v>
       </c>
       <c r="D32" t="n">
-        <v>0.757</v>
+        <v>3.472</v>
       </c>
       <c r="E32" t="n">
-        <v>1.135</v>
+        <v>5.889</v>
       </c>
       <c r="F32" t="n">
-        <v>0.73</v>
+        <v>0.278</v>
       </c>
       <c r="G32" t="n">
-        <v>1.919</v>
+        <v>0.917</v>
       </c>
       <c r="H32" t="n">
-        <v>0.216</v>
+        <v>0.889</v>
       </c>
       <c r="I32" t="n">
-        <v>0.243</v>
+        <v>1.167</v>
       </c>
       <c r="J32" t="n">
-        <v>0.297</v>
+        <v>1.333</v>
       </c>
       <c r="K32" t="n">
-        <v>1.486</v>
+        <v>2.056</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8110000000000001</v>
+        <v>1.194</v>
       </c>
       <c r="M32" t="n">
-        <v>0.514</v>
+        <v>0.917</v>
       </c>
       <c r="N32" t="n">
-        <v>0.378</v>
+        <v>0.25</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.243</v>
+        <v>0.861</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.243</v>
+        <v>0.861</v>
       </c>
       <c r="R32" t="n">
-        <v>1.054</v>
+        <v>2.028</v>
       </c>
       <c r="S32" t="n">
-        <v>0.216</v>
+        <v>1.5</v>
       </c>
       <c r="T32" t="n">
-        <v>175</v>
+        <v>349</v>
       </c>
       <c r="U32" t="n">
-        <v>0.405</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.514</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.784</v>
+        <v>2.111</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.973</v>
+        <v>2.333</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.806</v>
+        <v>0.905</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.189</v>
+        <v>1.556</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.351</v>
+        <v>2.944</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.538</v>
+        <v>0.528</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>0.694</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.027</v>
+        <v>1.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.649</v>
+        <v>0.278</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.649</v>
+        <v>0.917</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.393</v>
+        <v>0.303</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>25:17</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>3.404</v>
+        <v>8.18</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.606</v>
+        <v>0.571</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.62</v>
+        <v>0.592</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.151</v>
+        <v>1.059</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.131</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.222</v>
+        <v>1.548</v>
       </c>
       <c r="AV32" t="n">
-        <v>12.556</v>
+        <v>7.903</v>
       </c>
       <c r="AW32" t="n">
-        <v>13.778</v>
+        <v>9.452</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.065</v>
+        <v>0.187</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.038</v>
+        <v>0.067</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.073</v>
+        <v>0.122</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.01</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#6 J. VESELY (Per Game)</t>
+          <t>#8 D. BRIZUELA (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>8.667</v>
+        <v>9.167</v>
       </c>
       <c r="D33" t="n">
-        <v>3.472</v>
+        <v>2.139</v>
       </c>
       <c r="E33" t="n">
-        <v>5.889</v>
+        <v>3.806</v>
       </c>
       <c r="F33" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="T33" t="n">
+        <v>238</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.278</v>
       </c>
-      <c r="G33" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2.056</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.194</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.861</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.028</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>349</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="AH33" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>0.667</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.944</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.111</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.556</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.944</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.694</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
       <c r="AK33" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AO33" t="n">
+        <v>8.922000000000001</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>9.879</v>
+      </c>
+      <c r="AX33" t="n">
         <v>0.278</v>
       </c>
-      <c r="AL33" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>38:24</t>
-        </is>
-      </c>
-      <c r="AO33" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.592</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.059</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>1.548</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>7.903</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>9.452</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0.102</v>
-      </c>
       <c r="AY33" t="n">
-        <v>0.037</v>
+        <v>0.013</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.067</v>
+        <v>0.078</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.049</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#8 D. BRIZUELA (Per Game)</t>
+          <t>#13 T. SATORANSKY (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" t="n">
-        <v>9.167</v>
+        <v>7.086</v>
       </c>
       <c r="D34" t="n">
-        <v>2.139</v>
+        <v>1.2</v>
       </c>
       <c r="E34" t="n">
-        <v>3.806</v>
+        <v>2.4</v>
       </c>
       <c r="F34" t="n">
-        <v>1.389</v>
+        <v>1.257</v>
       </c>
       <c r="G34" t="n">
-        <v>3.833</v>
+        <v>2.543</v>
       </c>
       <c r="H34" t="n">
-        <v>0.722</v>
+        <v>0.914</v>
       </c>
       <c r="I34" t="n">
-        <v>0.833</v>
+        <v>1.229</v>
       </c>
       <c r="J34" t="n">
-        <v>1.417</v>
+        <v>4.314</v>
       </c>
       <c r="K34" t="n">
-        <v>0.972</v>
+        <v>2.686</v>
       </c>
       <c r="L34" t="n">
-        <v>0.167</v>
+        <v>0.857</v>
       </c>
       <c r="M34" t="n">
-        <v>0.583</v>
+        <v>0.743</v>
       </c>
       <c r="N34" t="n">
-        <v>0.139</v>
+        <v>0.286</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.917</v>
+        <v>1.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.833</v>
+        <v>1.257</v>
       </c>
       <c r="R34" t="n">
-        <v>1.778</v>
+        <v>1.914</v>
       </c>
       <c r="S34" t="n">
-        <v>1.083</v>
+        <v>1.714</v>
       </c>
       <c r="T34" t="n">
-        <v>238</v>
+        <v>405</v>
       </c>
       <c r="U34" t="n">
-        <v>1.611</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.722</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="W34" t="n">
-        <v>0.583</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="X34" t="n">
-        <v>0.278</v>
+        <v>0.029</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.417</v>
+        <v>1.371</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.694</v>
+        <v>1.571</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.836</v>
+        <v>0.873</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.306</v>
+        <v>0.657</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.333</v>
+        <v>1.543</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.426</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.139</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.278</v>
+        <v>0.429</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.111</v>
+        <v>0.286</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.167</v>
+        <v>0.457</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.278</v>
+        <v>0.971</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.667</v>
+        <v>2.086</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.348</v>
+        <v>0.466</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>34:23</t>
+          <t>24:49</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>8.922000000000001</v>
+        <v>6.883</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.553</v>
+        <v>0.624</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.573</v>
+        <v>0.646</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.027</v>
+        <v>1.029</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.103</v>
+        <v>0.203</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.095</v>
+        <v>0.185</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.545</v>
+        <v>3.082</v>
       </c>
       <c r="AV34" t="n">
-        <v>8.333</v>
+        <v>3.531</v>
       </c>
       <c r="AW34" t="n">
-        <v>9.879</v>
+        <v>6.612</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.125</v>
+        <v>0.133</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.006</v>
+        <v>0.041</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.035</v>
+        <v>0.135</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.052</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#13 T. SATORANSKY (Per Game)</t>
+          <t>#14 W. HERNANGOMEZ (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>7.086</v>
+        <v>5.5</v>
       </c>
       <c r="D35" t="n">
-        <v>1.2</v>
+        <v>1.842</v>
       </c>
       <c r="E35" t="n">
-        <v>2.4</v>
+        <v>3.605</v>
       </c>
       <c r="F35" t="n">
-        <v>1.257</v>
+        <v>0.026</v>
       </c>
       <c r="G35" t="n">
-        <v>2.543</v>
+        <v>0.105</v>
       </c>
       <c r="H35" t="n">
-        <v>0.914</v>
+        <v>1.737</v>
       </c>
       <c r="I35" t="n">
-        <v>1.229</v>
+        <v>2.579</v>
       </c>
       <c r="J35" t="n">
-        <v>4.314</v>
+        <v>0.421</v>
       </c>
       <c r="K35" t="n">
-        <v>2.686</v>
+        <v>2.368</v>
       </c>
       <c r="L35" t="n">
-        <v>0.857</v>
+        <v>1.342</v>
       </c>
       <c r="M35" t="n">
-        <v>0.743</v>
+        <v>0.342</v>
       </c>
       <c r="N35" t="n">
-        <v>0.286</v>
+        <v>0.632</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.257</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1.914</v>
+        <v>1.579</v>
       </c>
       <c r="S35" t="n">
-        <v>1.714</v>
+        <v>2.421</v>
       </c>
       <c r="T35" t="n">
-        <v>405</v>
+        <v>295</v>
       </c>
       <c r="U35" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0.743</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.457</v>
+        <v>0.105</v>
       </c>
       <c r="X35" t="n">
-        <v>0.229</v>
+        <v>0.053</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.371</v>
+        <v>2.947</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.571</v>
+        <v>3.711</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.873</v>
+        <v>0.794</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.657</v>
+        <v>0.632</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.543</v>
+        <v>1.553</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.426</v>
+        <v>0.407</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.2</v>
+        <v>0.079</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.457</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.971</v>
+        <v>0.026</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.086</v>
+        <v>0.105</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.466</v>
+        <v>0.25</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>46:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>6.883</v>
+        <v>5.845</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.624</v>
+        <v>0.507</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.646</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.029</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.203</v>
+        <v>0.171</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.185</v>
+        <v>0.468</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.082</v>
+        <v>0.421</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.531</v>
+        <v>3.711</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.612</v>
+        <v>4.132</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.216</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.022</v>
+        <v>0.122</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.073</v>
+        <v>0.226</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.152</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#14 W. HERNANGOMEZ (Per Game)</t>
+          <t>#17 J. NUNEZ (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>3.605</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.737</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2.579</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.421</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>2.368</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.342</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.342</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0.632</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5991,49 +5991,49 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.579</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.421</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.474</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.737</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.289</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.947</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.711</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.794</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.553</v>
+        <v>2</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.407</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -6048,901 +6048,901 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>26:09</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>5.845</v>
+        <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.507</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.5679999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.9409999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.171</v>
+        <v>0.333</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.468</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.421</v>
+        <v>1</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.711</v>
+        <v>2</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.132</v>
+        <v>3</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.107</v>
+        <v>0.274</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.113</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.015</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#17 J. NUNEZ (Per Game)</t>
+          <t>#19 Y. FALL (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1.455</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="E37" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="T37" t="n">
+        <v>84</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>03:54</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AU37" t="n">
         <v>2</v>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>25:16</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>1</v>
-      </c>
       <c r="AV37" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AW37" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.057</v>
+        <v>0.134</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.033</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#19 Y. FALL (Per Game)</t>
+          <t>#20 N. LAPROVITTOLA (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C38" t="n">
-        <v>1.455</v>
+        <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>0.636</v>
+        <v>1.1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.909</v>
+        <v>1.85</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="H38" t="n">
-        <v>0.182</v>
+        <v>1.15</v>
       </c>
       <c r="I38" t="n">
-        <v>0.273</v>
+        <v>1.25</v>
       </c>
       <c r="J38" t="n">
-        <v>0.121</v>
+        <v>3.85</v>
       </c>
       <c r="K38" t="n">
-        <v>0.697</v>
+        <v>0.95</v>
       </c>
       <c r="L38" t="n">
-        <v>0.424</v>
+        <v>0.15</v>
       </c>
       <c r="M38" t="n">
-        <v>0.061</v>
+        <v>0.7</v>
       </c>
       <c r="N38" t="n">
-        <v>0.121</v>
+        <v>0.25</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.061</v>
+        <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.061</v>
+        <v>2.05</v>
       </c>
       <c r="R38" t="n">
-        <v>0.394</v>
+        <v>2.05</v>
       </c>
       <c r="S38" t="n">
-        <v>0.485</v>
+        <v>2</v>
       </c>
       <c r="T38" t="n">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.152</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.606</v>
+        <v>1.65</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.697</v>
+        <v>1.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.87</v>
+        <v>0.892</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.182</v>
+        <v>0.6</v>
       </c>
       <c r="AC38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>0.333</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>06:58</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>1.09</v>
+        <v>8.85</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.7</v>
+        <v>0.548</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.707</v>
+        <v>0.588</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.335</v>
+        <v>0.904</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.056</v>
+        <v>0.232</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.2</v>
+        <v>0.184</v>
       </c>
       <c r="AU38" t="n">
-        <v>2</v>
+        <v>1.878</v>
       </c>
       <c r="AV38" t="n">
-        <v>15</v>
+        <v>3.049</v>
       </c>
       <c r="AW38" t="n">
-        <v>17</v>
+        <v>4.927</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.075</v>
+        <v>0.258</v>
       </c>
       <c r="AY38" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="AZ38" t="n">
-        <v>0.125</v>
-      </c>
       <c r="BA38" t="n">
-        <v>0.004</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#20 N. LAPROVITTOLA (Per Game)</t>
+          <t>#21 W. CLYBURN (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>13.419</v>
       </c>
       <c r="D39" t="n">
-        <v>1.1</v>
+        <v>2.71</v>
       </c>
       <c r="E39" t="n">
-        <v>1.85</v>
+        <v>5.097</v>
       </c>
       <c r="F39" t="n">
-        <v>1.55</v>
+        <v>1.839</v>
       </c>
       <c r="G39" t="n">
-        <v>4.4</v>
+        <v>4.935</v>
       </c>
       <c r="H39" t="n">
-        <v>1.15</v>
+        <v>2.484</v>
       </c>
       <c r="I39" t="n">
-        <v>1.25</v>
+        <v>3.355</v>
       </c>
       <c r="J39" t="n">
-        <v>3.85</v>
+        <v>1.581</v>
       </c>
       <c r="K39" t="n">
-        <v>0.95</v>
+        <v>3.161</v>
       </c>
       <c r="L39" t="n">
-        <v>0.15</v>
+        <v>0.806</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7</v>
+        <v>1.065</v>
       </c>
       <c r="N39" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.05</v>
+        <v>1.677</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.05</v>
+        <v>1.613</v>
       </c>
       <c r="R39" t="n">
-        <v>2.05</v>
+        <v>1.613</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>3.935</v>
       </c>
       <c r="T39" t="n">
-        <v>162</v>
+        <v>453</v>
       </c>
       <c r="U39" t="n">
-        <v>0.85</v>
+        <v>0.129</v>
       </c>
       <c r="V39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.65</v>
+        <v>3.871</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.85</v>
+        <v>4.71</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.892</v>
+        <v>0.822</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.6</v>
+        <v>1.161</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.15</v>
+        <v>2.484</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.522</v>
+        <v>0.468</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.05</v>
+        <v>0.258</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.15</v>
+        <v>0.452</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.333</v>
+        <v>0.571</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.5</v>
+        <v>1.581</v>
       </c>
       <c r="AL39" t="n">
-        <v>4.25</v>
+        <v>4.484</v>
       </c>
       <c r="AM39" t="n">
         <v>0.353</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>33:57</t>
+          <t>25:08</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>8.85</v>
+        <v>13.186</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.548</v>
+        <v>0.545</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.588</v>
+        <v>0.583</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.904</v>
+        <v>1.018</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.232</v>
+        <v>0.127</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.184</v>
+        <v>0.248</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.878</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="AV39" t="n">
-        <v>3.049</v>
+        <v>5.981</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.927</v>
+        <v>6.923</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.125</v>
+        <v>0.252</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.005</v>
+        <v>0.038</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.035</v>
+        <v>0.157</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.137</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#21 W. CLYBURN (Per Game)</t>
+          <t>#23 T. SHENGELIA (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C40" t="n">
-        <v>13.419</v>
+        <v>12.5</v>
       </c>
       <c r="D40" t="n">
-        <v>2.71</v>
+        <v>3.812</v>
       </c>
       <c r="E40" t="n">
-        <v>5.097</v>
+        <v>6.438</v>
       </c>
       <c r="F40" t="n">
-        <v>1.839</v>
+        <v>0.656</v>
       </c>
       <c r="G40" t="n">
-        <v>4.935</v>
+        <v>1.812</v>
       </c>
       <c r="H40" t="n">
-        <v>2.484</v>
+        <v>2.906</v>
       </c>
       <c r="I40" t="n">
-        <v>3.355</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
-        <v>1.581</v>
+        <v>2.656</v>
       </c>
       <c r="K40" t="n">
-        <v>3.161</v>
+        <v>2.969</v>
       </c>
       <c r="L40" t="n">
-        <v>0.806</v>
+        <v>1.531</v>
       </c>
       <c r="M40" t="n">
-        <v>1.065</v>
+        <v>0.75</v>
       </c>
       <c r="N40" t="n">
-        <v>0.29</v>
+        <v>0.844</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.677</v>
+        <v>1.844</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.613</v>
+        <v>1.719</v>
       </c>
       <c r="R40" t="n">
-        <v>1.613</v>
+        <v>2.5</v>
       </c>
       <c r="S40" t="n">
-        <v>3.935</v>
+        <v>4.312</v>
       </c>
       <c r="T40" t="n">
-        <v>453</v>
+        <v>539</v>
       </c>
       <c r="U40" t="n">
-        <v>1.968</v>
+        <v>0.094</v>
       </c>
       <c r="V40" t="n">
-        <v>1.419</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.645</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.871</v>
+        <v>5.344</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.71</v>
+        <v>6.469</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.822</v>
+        <v>0.826</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.161</v>
+        <v>1.344</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.484</v>
+        <v>2.719</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.468</v>
+        <v>0.494</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.161</v>
+        <v>0.031</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.387</v>
+        <v>0.156</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.417</v>
+        <v>0.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.452</v>
+        <v>0.094</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.581</v>
+        <v>0.656</v>
       </c>
       <c r="AL40" t="n">
-        <v>4.484</v>
+        <v>1.719</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.353</v>
+        <v>0.382</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>50:51</t>
+          <t>24:54</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>13.186</v>
+        <v>11.634</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.545</v>
+        <v>0.581</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.583</v>
+        <v>0.638</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.018</v>
+        <v>1.074</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.127</v>
+        <v>0.158</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.248</v>
+        <v>0.352</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.441</v>
       </c>
       <c r="AV40" t="n">
-        <v>5.981</v>
+        <v>4.475</v>
       </c>
       <c r="AW40" t="n">
-        <v>6.923</v>
+        <v>5.915</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.125</v>
+        <v>0.225</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.019</v>
+        <v>0.073</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.077</v>
+        <v>0.148</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.06</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#23 T. SHENGELIA (Per Game)</t>
+          <t>#41 S. KEITA (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C41" t="n">
-        <v>12.5</v>
+        <v>1.667</v>
       </c>
       <c r="D41" t="n">
-        <v>3.812</v>
+        <v>0.778</v>
       </c>
       <c r="E41" t="n">
-        <v>6.438</v>
+        <v>1.333</v>
       </c>
       <c r="F41" t="n">
-        <v>0.656</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.812</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.906</v>
+        <v>0.111</v>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>0.222</v>
       </c>
       <c r="J41" t="n">
-        <v>2.656</v>
+        <v>0.111</v>
       </c>
       <c r="K41" t="n">
-        <v>2.969</v>
+        <v>0.556</v>
       </c>
       <c r="L41" t="n">
-        <v>1.531</v>
+        <v>0.444</v>
       </c>
       <c r="M41" t="n">
-        <v>0.75</v>
+        <v>0.333</v>
       </c>
       <c r="N41" t="n">
-        <v>0.844</v>
+        <v>0.222</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.844</v>
+        <v>0.444</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.719</v>
+        <v>0.444</v>
       </c>
       <c r="R41" t="n">
-        <v>2.5</v>
+        <v>0.556</v>
       </c>
       <c r="S41" t="n">
-        <v>4.312</v>
+        <v>0.444</v>
       </c>
       <c r="T41" t="n">
-        <v>539</v>
+        <v>19</v>
       </c>
       <c r="U41" t="n">
-        <v>1.406</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.688</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.531</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>5.344</v>
+        <v>0.778</v>
       </c>
       <c r="Z41" t="n">
-        <v>6.469</v>
+        <v>0.889</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.826</v>
+        <v>0.875</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.344</v>
+        <v>0.111</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.719</v>
+        <v>0.556</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.494</v>
+        <v>0.2</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
         <v>0</v>
       </c>
       <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="AO41" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AY41" t="n">
         <v>0.094</v>
       </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.719</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>47:01</t>
-        </is>
-      </c>
-      <c r="AO41" t="n">
-        <v>11.634</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.074</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>1.441</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>4.475</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>5.915</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0.038</v>
-      </c>
       <c r="AZ41" t="n">
-        <v>0.079</v>
+        <v>0.124</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.101</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#41 S. KEITA (Per Game)</t>
+          <t>#43 N. KUSTURICA (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.333</v>
+        <v>0.25</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -6951,49 +6951,49 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.222</v>
+        <v>0.25</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -7002,22 +7002,22 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.556</v>
+        <v>0.25</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7048,111 +7048,111 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>00:17</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>1.876</v>
+        <v>0.25</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.583</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.582</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.237</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.08</v>
+        <v>0.424</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#43 N. KUSTURICA (Per Game)</t>
+          <t>#44 J. PARRA (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>5.789</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1.658</v>
       </c>
       <c r="E43" t="n">
-        <v>0.25</v>
+        <v>2.763</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1.737</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.895</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1.132</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2.263</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.263</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="N43" t="n">
-        <v>0.25</v>
+        <v>0.289</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>0.553</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.737</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -7167,420 +7167,420 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.711</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.158</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>0.793</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>0.789</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.25</v>
+        <v>1.421</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>0.447</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.553</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>0.288</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>00:17</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>0.25</v>
+        <v>5.551</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>0.544</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.043</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>8.143000000000001</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>9.952</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.418</v>
+        <v>0.142</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#44 J. PARRA (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>38</v>
       </c>
       <c r="C44" t="n">
-        <v>5.789</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>1.658</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>2.763</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.737</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.895</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1.132</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2.263</v>
+        <v>1.395</v>
       </c>
       <c r="L44" t="n">
-        <v>1.263</v>
+        <v>1.842</v>
       </c>
       <c r="M44" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0.289</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.553</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.395</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.737</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.158</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0.474</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.211</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.789</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.711</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.158</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.793</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.789</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.421</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.184</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.447</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.553</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.288</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>39:25</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>5.551</v>
+        <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.544</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.043</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>8.143000000000001</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>9.952</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>38</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>84.76300000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>21.132</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>38.395</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>9.632</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>25.737</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>13.605</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>17.289</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>18.211</v>
       </c>
       <c r="K45" t="n">
-        <v>1.395</v>
+        <v>21.947</v>
       </c>
       <c r="L45" t="n">
-        <v>1.842</v>
+        <v>11.132</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>7.132</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.895</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.6840000000000001</v>
+        <v>12</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>10.605</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>18.632</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>20.447</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3794</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>23.579</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>28.211</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>0.836</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>9.553000000000001</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>19.816</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>0.482</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.605</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>3.974</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>0.404</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>0.974</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>2.079</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.468</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>8.657999999999999</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>23.658</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>0.366</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:18</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>83.739</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>0.555</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.012</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>1.518</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>5.344</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>6.862</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="BA45" t="n">
         <v>0</v>
@@ -7589,495 +7589,165 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>38</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>83.86799999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>21.711</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>37.632</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>8.316000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>23.605</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>19.763</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>17.316</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>22.947</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>10.368</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>5.974</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.895</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>12.974</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>11.579</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>18.974</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>20.132</v>
       </c>
       <c r="T46" t="n">
-        <v>97</v>
+        <v>3689</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>27.474</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>32.079</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>0.856</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>8.842000000000001</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>18.658</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>0.474</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>0.895</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.395</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>0.374</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>0.921</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>2.289</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>7.395</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>21.316</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:18</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>0.6840000000000001</v>
+        <v>82.90600000000001</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.012</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>1.335</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>6.055</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>38</v>
-      </c>
-      <c r="C47" t="n">
-        <v>84.76300000000001</v>
-      </c>
-      <c r="D47" t="n">
-        <v>21.132</v>
-      </c>
-      <c r="E47" t="n">
-        <v>38.395</v>
-      </c>
-      <c r="F47" t="n">
-        <v>9.632</v>
-      </c>
-      <c r="G47" t="n">
-        <v>25.737</v>
-      </c>
-      <c r="H47" t="n">
-        <v>13.605</v>
-      </c>
-      <c r="I47" t="n">
-        <v>17.289</v>
-      </c>
-      <c r="J47" t="n">
-        <v>18.211</v>
-      </c>
-      <c r="K47" t="n">
-        <v>21.947</v>
-      </c>
-      <c r="L47" t="n">
-        <v>11.132</v>
-      </c>
-      <c r="M47" t="n">
-        <v>7.132</v>
-      </c>
-      <c r="N47" t="n">
-        <v>3.895</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>10.605</v>
-      </c>
-      <c r="R47" t="n">
-        <v>18.632</v>
-      </c>
-      <c r="S47" t="n">
-        <v>20.447</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3794</v>
-      </c>
-      <c r="U47" t="n">
-        <v>9.895</v>
-      </c>
-      <c r="V47" t="n">
-        <v>12.132</v>
-      </c>
-      <c r="W47" t="n">
-        <v>6.974</v>
-      </c>
-      <c r="X47" t="n">
-        <v>4.079</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>23.579</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>28.211</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>9.553000000000001</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>19.816</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.605</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>3.974</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>2.079</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>8.657999999999999</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>23.658</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>201:18</t>
-        </is>
-      </c>
-      <c r="AO47" t="n">
-        <v>83.739</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>1.012</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>1.518</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>5.344</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>6.862</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>38</v>
-      </c>
-      <c r="C48" t="n">
-        <v>83.86799999999999</v>
-      </c>
-      <c r="D48" t="n">
-        <v>21.711</v>
-      </c>
-      <c r="E48" t="n">
-        <v>37.632</v>
-      </c>
-      <c r="F48" t="n">
-        <v>8.316000000000001</v>
-      </c>
-      <c r="G48" t="n">
-        <v>23.605</v>
-      </c>
-      <c r="H48" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I48" t="n">
-        <v>19.763</v>
-      </c>
-      <c r="J48" t="n">
-        <v>17.316</v>
-      </c>
-      <c r="K48" t="n">
-        <v>22.947</v>
-      </c>
-      <c r="L48" t="n">
-        <v>10.368</v>
-      </c>
-      <c r="M48" t="n">
-        <v>5.974</v>
-      </c>
-      <c r="N48" t="n">
-        <v>3.895</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>12.974</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>11.553</v>
-      </c>
-      <c r="R48" t="n">
-        <v>18.974</v>
-      </c>
-      <c r="S48" t="n">
-        <v>20.132</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3689</v>
-      </c>
-      <c r="U48" t="n">
-        <v>8.289</v>
-      </c>
-      <c r="V48" t="n">
-        <v>11</v>
-      </c>
-      <c r="W48" t="n">
-        <v>8.553000000000001</v>
-      </c>
-      <c r="X48" t="n">
-        <v>4.921</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>27.474</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>32.079</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.856</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>8.842000000000001</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>18.658</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0.921</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>2.289</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>7.395</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>21.316</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>201:18</t>
-        </is>
-      </c>
-      <c r="AO48" t="n">
-        <v>82.90600000000001</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.012</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>1.335</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>6.055</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="BA48" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FC BARCELONA.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FC BARCELONA.xlsx
@@ -671,13 +671,13 @@
         <v>0.2121460812474354</v>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>400</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>465</v>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>283</v>
       </c>
       <c r="M2" t="n">
         <v>403</v>
@@ -752,13 +752,13 @@
         <v>1.117766497461929</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01825557809330629</v>
+        <v>0.8113590263691683</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01654846335697399</v>
+        <v>1.099290780141844</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.5</v>
+        <v>1.699386503067485</v>
       </c>
       <c r="AN2" t="n">
         <v>1.517543859649123</v>
@@ -801,13 +801,13 @@
         <v>0.2121460812474354</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2368421052631579</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1842105263157895</v>
+        <v>12.23684210526316</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3947368421052632</v>
+        <v>7.447368421052632</v>
       </c>
       <c r="M3" t="n">
         <v>10.60526315789474</v>
@@ -882,13 +882,13 @@
         <v>1.117766497461929</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01825557809330629</v>
+        <v>0.8113590263691685</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01654846335697399</v>
+        <v>1.099290780141844</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.5</v>
+        <v>1.699386503067485</v>
       </c>
       <c r="AN3" t="n">
         <v>1.517543859649123</v>
@@ -931,13 +931,13 @@
         <v>0.2531155994843146</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>428</v>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>337</v>
       </c>
       <c r="M4" t="n">
         <v>440</v>
@@ -1012,13 +1012,13 @@
         <v>1.067403314917127</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03289473684210526</v>
+        <v>0.7390350877192983</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01015228426395939</v>
+        <v>1.086294416243655</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.2</v>
+        <v>1.717171717171717</v>
       </c>
       <c r="AN4" t="n">
         <v>1.334685598377282</v>
@@ -1061,13 +1061,13 @@
         <v>0.2531155994843146</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3947368421052632</v>
+        <v>8.868421052631579</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1052631578947368</v>
+        <v>11.26315789473684</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2894736842105263</v>
+        <v>8.868421052631579</v>
       </c>
       <c r="M5" t="n">
         <v>11.57894736842105</v>
@@ -1142,13 +1142,13 @@
         <v>1.067403314917127</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.03289473684210526</v>
+        <v>0.7390350877192983</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01015228426395939</v>
+        <v>1.086294416243655</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.2</v>
+        <v>1.717171717171717</v>
       </c>
       <c r="AN5" t="n">
         <v>1.334685598377282</v>
@@ -1486,16 +1486,16 @@
         <v>533</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="W8" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="Y8" t="n">
         <v>132</v>
@@ -1651,16 +1651,16 @@
         <v>44</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>5</v>
@@ -1816,16 +1816,16 @@
         <v>118</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="n">
         <v>27</v>
@@ -1981,16 +1981,16 @@
         <v>175</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y11" t="n">
         <v>29</v>
@@ -2146,16 +2146,16 @@
         <v>349</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="n">
         <v>76</v>
@@ -2311,16 +2311,16 @@
         <v>238</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
         <v>51</v>
@@ -2476,16 +2476,16 @@
         <v>405</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="V14" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="n">
         <v>48</v>
@@ -2641,16 +2641,16 @@
         <v>295</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="W15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y15" t="n">
         <v>112</v>
@@ -2974,13 +2974,13 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="n">
         <v>20</v>
@@ -3136,16 +3136,16 @@
         <v>162</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y18" t="n">
         <v>33</v>
@@ -3301,16 +3301,16 @@
         <v>453</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y19" t="n">
         <v>120</v>
@@ -3466,16 +3466,16 @@
         <v>539</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Y20" t="n">
         <v>171</v>
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -3961,16 +3961,16 @@
         <v>283</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
         <v>65</v>
@@ -4291,16 +4291,16 @@
         <v>3794</v>
       </c>
       <c r="U25" t="n">
-        <v>9</v>
+        <v>397</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>464</v>
       </c>
       <c r="W25" t="n">
-        <v>15</v>
+        <v>277</v>
       </c>
       <c r="X25" t="n">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="Y25" t="n">
         <v>896</v>
@@ -4456,16 +4456,16 @@
         <v>3689</v>
       </c>
       <c r="U26" t="n">
-        <v>15</v>
+        <v>332</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>423</v>
       </c>
       <c r="W26" t="n">
-        <v>11</v>
+        <v>340</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>198</v>
       </c>
       <c r="Y26" t="n">
         <v>1044</v>
@@ -4680,16 +4680,16 @@
         <v>533</v>
       </c>
       <c r="U28" t="n">
-        <v>0.054</v>
+        <v>2.108</v>
       </c>
       <c r="V28" t="n">
-        <v>0.054</v>
+        <v>1.162</v>
       </c>
       <c r="W28" t="n">
-        <v>0.162</v>
+        <v>1.405</v>
       </c>
       <c r="X28" t="n">
-        <v>0.054</v>
+        <v>0.784</v>
       </c>
       <c r="Y28" t="n">
         <v>3.568</v>
@@ -4845,16 +4845,16 @@
         <v>44</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="Y29" t="n">
         <v>0.156</v>
@@ -5010,16 +5010,16 @@
         <v>118</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>0.459</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.297</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="Y30" t="n">
         <v>0.73</v>
@@ -5175,16 +5175,16 @@
         <v>175</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.405</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="W31" t="n">
-        <v>0.054</v>
+        <v>0.514</v>
       </c>
       <c r="X31" t="n">
-        <v>0.027</v>
+        <v>0.189</v>
       </c>
       <c r="Y31" t="n">
         <v>0.784</v>
@@ -5340,16 +5340,16 @@
         <v>349</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.944</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y32" t="n">
         <v>2.111</v>
@@ -5505,16 +5505,16 @@
         <v>238</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.722</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="Y33" t="n">
         <v>1.417</v>
@@ -5670,16 +5670,16 @@
         <v>405</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V34" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="W34" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.457</v>
       </c>
       <c r="X34" t="n">
-        <v>0.029</v>
+        <v>0.229</v>
       </c>
       <c r="Y34" t="n">
         <v>1.371</v>
@@ -5835,16 +5835,16 @@
         <v>295</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.737</v>
       </c>
       <c r="W35" t="n">
-        <v>0.105</v>
+        <v>0.342</v>
       </c>
       <c r="X35" t="n">
-        <v>0.053</v>
+        <v>0.316</v>
       </c>
       <c r="Y35" t="n">
         <v>2.947</v>
@@ -6168,13 +6168,13 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.061</v>
+        <v>0.545</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="Y37" t="n">
         <v>0.606</v>
@@ -6330,16 +6330,16 @@
         <v>162</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="Y38" t="n">
         <v>1.65</v>
@@ -6495,16 +6495,16 @@
         <v>453</v>
       </c>
       <c r="U39" t="n">
-        <v>0.129</v>
+        <v>2.032</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.484</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.355</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="Y39" t="n">
         <v>3.871</v>
@@ -6660,16 +6660,16 @@
         <v>539</v>
       </c>
       <c r="U40" t="n">
-        <v>0.094</v>
+        <v>1.594</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.688</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.562</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.031</v>
       </c>
       <c r="Y40" t="n">
         <v>5.344</v>
@@ -6828,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -7155,16 +7155,16 @@
         <v>283</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>0.474</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.105</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.789</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="Y43" t="n">
         <v>1.711</v>
@@ -7485,16 +7485,16 @@
         <v>3794</v>
       </c>
       <c r="U45" t="n">
-        <v>0.237</v>
+        <v>10.447</v>
       </c>
       <c r="V45" t="n">
-        <v>0.184</v>
+        <v>12.211</v>
       </c>
       <c r="W45" t="n">
-        <v>0.395</v>
+        <v>7.289</v>
       </c>
       <c r="X45" t="n">
-        <v>0.158</v>
+        <v>4.289</v>
       </c>
       <c r="Y45" t="n">
         <v>23.579</v>
@@ -7650,16 +7650,16 @@
         <v>3689</v>
       </c>
       <c r="U46" t="n">
-        <v>0.395</v>
+        <v>8.737</v>
       </c>
       <c r="V46" t="n">
-        <v>0.105</v>
+        <v>11.132</v>
       </c>
       <c r="W46" t="n">
-        <v>0.289</v>
+        <v>8.946999999999999</v>
       </c>
       <c r="X46" t="n">
-        <v>0.132</v>
+        <v>5.211</v>
       </c>
       <c r="Y46" t="n">
         <v>27.474</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FC BARCELONA.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_FC BARCELONA.xlsx
@@ -683,13 +683,13 @@
         <v>403</v>
       </c>
       <c r="N2" t="n">
-        <v>895</v>
+        <v>380</v>
       </c>
       <c r="O2" t="n">
-        <v>1077</v>
+        <v>562</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4419368075502667</v>
+        <v>0.2306114074681986</v>
       </c>
       <c r="Q2" t="n">
         <v>360</v>
@@ -710,25 +710,25 @@
         <v>0.06196142798522774</v>
       </c>
       <c r="W2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03364792778005745</v>
+        <v>0.0389823553549446</v>
       </c>
       <c r="Z2" t="n">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="AA2" t="n">
-        <v>903</v>
+        <v>890</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3705375461633156</v>
+        <v>0.3652031185884284</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8310120705663882</v>
+        <v>0.6761565836298933</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4825737265415549</v>
@@ -737,13 +737,13 @@
         <v>0.4105960264900662</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3643410852713178</v>
+        <v>0.3617977528089887</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.662024141132776</v>
+        <v>1.352313167259787</v>
       </c>
       <c r="AI2" t="n">
         <v>0.8211920529801324</v>
@@ -813,13 +813,13 @@
         <v>10.60526315789474</v>
       </c>
       <c r="N3" t="n">
-        <v>23.55263157894737</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>28.34210526315789</v>
+        <v>14.78947368421053</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4419368075502668</v>
+        <v>0.2306114074681986</v>
       </c>
       <c r="Q3" t="n">
         <v>9.473684210526315</v>
@@ -840,25 +840,25 @@
         <v>0.06196142798522775</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>1.184210526315789</v>
       </c>
       <c r="X3" t="n">
-        <v>2.157894736842105</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03364792778005746</v>
+        <v>0.03898235535494461</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.657894736842104</v>
+        <v>8.473684210526315</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.76315789473684</v>
+        <v>23.42105263157895</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3705375461633156</v>
+        <v>0.3652031185884285</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8310120705663882</v>
+        <v>0.6761565836298933</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4825737265415549</v>
@@ -867,13 +867,13 @@
         <v>0.4105960264900662</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4634146341463414</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3643410852713178</v>
+        <v>0.3617977528089887</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.662024141132776</v>
+        <v>1.352313167259787</v>
       </c>
       <c r="AI3" t="n">
         <v>0.8211920529801324</v>
@@ -943,13 +943,13 @@
         <v>440</v>
       </c>
       <c r="N4" t="n">
-        <v>1052</v>
+        <v>455</v>
       </c>
       <c r="O4" t="n">
-        <v>1229</v>
+        <v>632</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5281478298238075</v>
+        <v>0.2715943274602493</v>
       </c>
       <c r="Q4" t="n">
         <v>334</v>
@@ -970,25 +970,25 @@
         <v>0.03867640739149119</v>
       </c>
       <c r="W4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03867640739149119</v>
+        <v>0.04340352385045122</v>
       </c>
       <c r="Z4" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AA4" t="n">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.350236355822948</v>
+        <v>0.345509239363988</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8559804719283971</v>
+        <v>0.7199367088607594</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4791965566714491</v>
@@ -997,13 +997,13 @@
         <v>0.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4</v>
+        <v>0.405940594059406</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.350920245398773</v>
+        <v>0.349502487562189</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.711960943856794</v>
+        <v>1.439873417721519</v>
       </c>
       <c r="AI4" t="n">
         <v>0.8</v>
@@ -1073,13 +1073,13 @@
         <v>11.57894736842105</v>
       </c>
       <c r="N5" t="n">
-        <v>27.68421052631579</v>
+        <v>11.97368421052632</v>
       </c>
       <c r="O5" t="n">
-        <v>32.3421052631579</v>
+        <v>16.63157894736842</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5281478298238076</v>
+        <v>0.2715943274602493</v>
       </c>
       <c r="Q5" t="n">
         <v>8.789473684210526</v>
@@ -1100,25 +1100,25 @@
         <v>0.03867640739149119</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9473684210526315</v>
+        <v>1.078947368421053</v>
       </c>
       <c r="X5" t="n">
-        <v>2.368421052631579</v>
+        <v>2.657894736842105</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03867640739149119</v>
+        <v>0.04340352385045123</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.526315789473684</v>
+        <v>7.394736842105263</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.44736842105263</v>
+        <v>21.15789473684211</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.350236355822948</v>
+        <v>0.345509239363988</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8559804719283971</v>
+        <v>0.7199367088607594</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4791965566714491</v>
@@ -1127,13 +1127,13 @@
         <v>0.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4</v>
+        <v>0.405940594059406</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.350920245398773</v>
+        <v>0.349502487562189</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.711960943856794</v>
+        <v>1.439873417721519</v>
       </c>
       <c r="AI5" t="n">
         <v>0.8</v>
@@ -1498,13 +1498,13 @@
         <v>29</v>
       </c>
       <c r="Y8" t="n">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="Z8" t="n">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.88</v>
+        <v>0.591</v>
       </c>
       <c r="AB8" t="n">
         <v>67</v>
@@ -1525,22 +1525,22 @@
         <v>0.419</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AK8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AL8" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.413</v>
+        <v>0.409</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.844</v>
+        <v>0.737</v>
       </c>
       <c r="AB10" t="n">
         <v>10</v>
@@ -1993,13 +1993,13 @@
         <v>7</v>
       </c>
       <c r="Y11" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.806</v>
+        <v>0.75</v>
       </c>
       <c r="AB11" t="n">
         <v>7</v>
@@ -2020,22 +2020,22 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.3</v>
+        <v>0.385</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.393</v>
+        <v>0.379</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         <v>6</v>
       </c>
       <c r="Y12" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="Z12" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.905</v>
+        <v>0.846</v>
       </c>
       <c r="AB12" t="n">
         <v>56</v>
@@ -2323,13 +2323,13 @@
         <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="Z13" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.836</v>
+        <v>0.714</v>
       </c>
       <c r="AB13" t="n">
         <v>47</v>
@@ -2350,22 +2350,22 @@
         <v>0.278</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="AK13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AL13" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         <v>8</v>
       </c>
       <c r="Y14" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.873</v>
+        <v>0.696</v>
       </c>
       <c r="AB14" t="n">
         <v>23</v>
@@ -2653,13 +2653,13 @@
         <v>12</v>
       </c>
       <c r="Y15" t="n">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="Z15" t="n">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.794</v>
+        <v>0.613</v>
       </c>
       <c r="AB15" t="n">
         <v>24</v>
@@ -2983,13 +2983,13 @@
         <v>4</v>
       </c>
       <c r="Y17" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.87</v>
+        <v>0.824</v>
       </c>
       <c r="AB17" t="n">
         <v>6</v>
@@ -3148,13 +3148,13 @@
         <v>9</v>
       </c>
       <c r="Y18" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.892</v>
+        <v>0.714</v>
       </c>
       <c r="AB18" t="n">
         <v>12</v>
@@ -3313,13 +3313,13 @@
         <v>22</v>
       </c>
       <c r="Y19" t="n">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="Z19" t="n">
-        <v>146</v>
+        <v>69</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.822</v>
+        <v>0.623</v>
       </c>
       <c r="AB19" t="n">
         <v>36</v>
@@ -3478,13 +3478,13 @@
         <v>33</v>
       </c>
       <c r="Y20" t="n">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="Z20" t="n">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.826</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB20" t="n">
         <v>43</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
@@ -3517,10 +3517,10 @@
         <v>21</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.382</v>
+        <v>0.389</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
@@ -3643,13 +3643,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z21" t="n">
         <v>7</v>
       </c>
-      <c r="Z21" t="n">
-        <v>8</v>
-      </c>
       <c r="AA21" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
       <c r="AB21" t="n">
         <v>1</v>
@@ -3973,13 +3973,13 @@
         <v>20</v>
       </c>
       <c r="Y23" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="Z23" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.793</v>
+        <v>0.646</v>
       </c>
       <c r="AB23" t="n">
         <v>30</v>
@@ -4000,22 +4000,22 @@
         <v>0.667</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AI23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.429</v>
+        <v>0.462</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.288</v>
+        <v>0.264</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -4303,13 +4303,13 @@
         <v>163</v>
       </c>
       <c r="Y25" t="n">
-        <v>896</v>
+        <v>379</v>
       </c>
       <c r="Z25" t="n">
-        <v>1072</v>
+        <v>555</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.836</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AB25" t="n">
         <v>363</v>
@@ -4330,22 +4330,22 @@
         <v>0.404</v>
       </c>
       <c r="AH25" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI25" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.468</v>
+        <v>0.478</v>
       </c>
       <c r="AK25" t="n">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="AL25" t="n">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.366</v>
+        <v>0.363</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
@@ -4468,13 +4468,13 @@
         <v>198</v>
       </c>
       <c r="Y26" t="n">
-        <v>1044</v>
+        <v>455</v>
       </c>
       <c r="Z26" t="n">
-        <v>1219</v>
+        <v>630</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.856</v>
+        <v>0.722</v>
       </c>
       <c r="AB26" t="n">
         <v>336</v>
@@ -4495,22 +4495,22 @@
         <v>0.374</v>
       </c>
       <c r="AH26" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AI26" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.402</v>
+        <v>0.408</v>
       </c>
       <c r="AK26" t="n">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AL26" t="n">
-        <v>810</v>
+        <v>799</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -4692,13 +4692,13 @@
         <v>0.784</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.568</v>
+        <v>0.703</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.054</v>
+        <v>1.189</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.88</v>
+        <v>0.591</v>
       </c>
       <c r="AB28" t="n">
         <v>1.811</v>
@@ -4719,22 +4719,22 @@
         <v>0.419</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.081</v>
+        <v>0.108</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.162</v>
+        <v>0.189</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.919</v>
+        <v>1.892</v>
       </c>
       <c r="AL28" t="n">
-        <v>4.649</v>
+        <v>4.622</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.413</v>
+        <v>0.409</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
@@ -5022,13 +5022,13 @@
         <v>0.054</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.73</v>
+        <v>0.378</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.865</v>
+        <v>0.514</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.844</v>
+        <v>0.737</v>
       </c>
       <c r="AB30" t="n">
         <v>0.27</v>
@@ -5187,13 +5187,13 @@
         <v>0.189</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.784</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.973</v>
+        <v>0.757</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.806</v>
+        <v>0.75</v>
       </c>
       <c r="AB31" t="n">
         <v>0.189</v>
@@ -5214,22 +5214,22 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.081</v>
+        <v>0.135</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.27</v>
+        <v>0.351</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.3</v>
+        <v>0.385</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.649</v>
+        <v>0.595</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.649</v>
+        <v>1.568</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.393</v>
+        <v>0.379</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
         <v>0.167</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.111</v>
+        <v>1.222</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.333</v>
+        <v>1.444</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.905</v>
+        <v>0.846</v>
       </c>
       <c r="AB32" t="n">
         <v>1.556</v>
@@ -5517,13 +5517,13 @@
         <v>0.278</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.417</v>
+        <v>0.694</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.694</v>
+        <v>0.972</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.836</v>
+        <v>0.714</v>
       </c>
       <c r="AB33" t="n">
         <v>1.306</v>
@@ -5544,22 +5544,22 @@
         <v>0.278</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.111</v>
+        <v>0.139</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.167</v>
+        <v>0.222</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.278</v>
+        <v>1.25</v>
       </c>
       <c r="AL33" t="n">
-        <v>3.667</v>
+        <v>3.611</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -5682,13 +5682,13 @@
         <v>0.229</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.371</v>
+        <v>0.457</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.571</v>
+        <v>0.657</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.873</v>
+        <v>0.696</v>
       </c>
       <c r="AB34" t="n">
         <v>0.657</v>
@@ -5847,13 +5847,13 @@
         <v>0.316</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.947</v>
+        <v>1.211</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.711</v>
+        <v>1.974</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.794</v>
+        <v>0.613</v>
       </c>
       <c r="AB35" t="n">
         <v>0.632</v>
@@ -6177,13 +6177,13 @@
         <v>0.121</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.606</v>
+        <v>0.424</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.697</v>
+        <v>0.515</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.87</v>
+        <v>0.824</v>
       </c>
       <c r="AB37" t="n">
         <v>0.182</v>
@@ -6342,13 +6342,13 @@
         <v>0.45</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.85</v>
+        <v>0.7</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.892</v>
+        <v>0.714</v>
       </c>
       <c r="AB38" t="n">
         <v>0.6</v>
@@ -6507,13 +6507,13 @@
         <v>0.71</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.871</v>
+        <v>1.387</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.71</v>
+        <v>2.226</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.822</v>
+        <v>0.623</v>
       </c>
       <c r="AB39" t="n">
         <v>1.161</v>
@@ -6672,13 +6672,13 @@
         <v>1.031</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.344</v>
+        <v>2.438</v>
       </c>
       <c r="Z40" t="n">
-        <v>6.469</v>
+        <v>3.562</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.826</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB40" t="n">
         <v>1.344</v>
@@ -6702,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.094</v>
+        <v>0.125</v>
       </c>
       <c r="AJ40" t="n">
         <v>0</v>
@@ -6711,10 +6711,10 @@
         <v>0.656</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.719</v>
+        <v>1.688</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.382</v>
+        <v>0.389</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
@@ -6837,13 +6837,13 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="Z41" t="n">
         <v>0.778</v>
       </c>
-      <c r="Z41" t="n">
-        <v>0.889</v>
-      </c>
       <c r="AA41" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
       <c r="AB41" t="n">
         <v>0.111</v>
@@ -7167,13 +7167,13 @@
         <v>0.526</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.711</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.158</v>
+        <v>1.263</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.793</v>
+        <v>0.646</v>
       </c>
       <c r="AB43" t="n">
         <v>0.789</v>
@@ -7194,22 +7194,22 @@
         <v>0.667</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.079</v>
+        <v>0.158</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.184</v>
+        <v>0.342</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.429</v>
+        <v>0.462</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.447</v>
+        <v>0.368</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.553</v>
+        <v>1.395</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.288</v>
+        <v>0.264</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
@@ -7497,13 +7497,13 @@
         <v>4.289</v>
       </c>
       <c r="Y45" t="n">
-        <v>23.579</v>
+        <v>9.974</v>
       </c>
       <c r="Z45" t="n">
-        <v>28.211</v>
+        <v>14.605</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.836</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AB45" t="n">
         <v>9.553000000000001</v>
@@ -7524,22 +7524,22 @@
         <v>0.404</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.974</v>
+        <v>1.158</v>
       </c>
       <c r="AI45" t="n">
-        <v>2.079</v>
+        <v>2.421</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.468</v>
+        <v>0.478</v>
       </c>
       <c r="AK45" t="n">
-        <v>8.657999999999999</v>
+        <v>8.474</v>
       </c>
       <c r="AL45" t="n">
-        <v>23.658</v>
+        <v>23.316</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.366</v>
+        <v>0.363</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
@@ -7662,13 +7662,13 @@
         <v>5.211</v>
       </c>
       <c r="Y46" t="n">
-        <v>27.474</v>
+        <v>11.974</v>
       </c>
       <c r="Z46" t="n">
-        <v>32.079</v>
+        <v>16.579</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.856</v>
+        <v>0.722</v>
       </c>
       <c r="AB46" t="n">
         <v>8.842000000000001</v>
@@ -7689,22 +7689,22 @@
         <v>0.374</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.921</v>
+        <v>1.053</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.289</v>
+        <v>2.579</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.402</v>
+        <v>0.408</v>
       </c>
       <c r="AK46" t="n">
-        <v>7.395</v>
+        <v>7.263</v>
       </c>
       <c r="AL46" t="n">
-        <v>21.316</v>
+        <v>21.026</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
